--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
@@ -2125,7 +2125,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:43</t>
+    <t xml:space="preserve">2026-09-07 12:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
@@ -2125,7 +2125,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:50</t>
+    <t xml:space="preserve">2026-09-08 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
